--- a/artfynd/A 51337-2024 artfynd.xlsx
+++ b/artfynd/A 51337-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121146592</v>
+        <v>121146575</v>
       </c>
       <c r="B2" t="n">
-        <v>98071</v>
+        <v>79682</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592533</v>
+        <v>592529</v>
       </c>
       <c r="R2" t="n">
-        <v>7056596</v>
+        <v>7056593</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121147479</v>
+        <v>121146679</v>
       </c>
       <c r="B3" t="n">
-        <v>95365</v>
+        <v>90662</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2869</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592613</v>
+        <v>592516</v>
       </c>
       <c r="R3" t="n">
-        <v>7056374</v>
+        <v>7056543</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121146483</v>
+        <v>121147431</v>
       </c>
       <c r="B4" t="n">
-        <v>57348</v>
+        <v>98081</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,31 +911,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -948,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592490</v>
+        <v>592617</v>
       </c>
       <c r="R4" t="n">
-        <v>7056655</v>
+        <v>7056397</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,12 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:41</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121146485</v>
+        <v>121146272</v>
       </c>
       <c r="B5" t="n">
-        <v>98071</v>
+        <v>79682</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,42 +1027,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592495</v>
+        <v>592457</v>
       </c>
       <c r="R5" t="n">
-        <v>7056643</v>
+        <v>7056760</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121146430</v>
+        <v>121146710</v>
       </c>
       <c r="B6" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,42 +1139,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592474</v>
+        <v>592531</v>
       </c>
       <c r="R6" t="n">
-        <v>7056672</v>
+        <v>7056489</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1230,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121146569</v>
+        <v>121146572</v>
       </c>
       <c r="B7" t="n">
-        <v>90973</v>
+        <v>91137</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,25 +1251,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1297,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592513</v>
+        <v>592530</v>
       </c>
       <c r="R7" t="n">
-        <v>7056596</v>
+        <v>7056612</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1369,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121146704</v>
+        <v>121146339</v>
       </c>
       <c r="B8" t="n">
-        <v>79679</v>
+        <v>91973</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,25 +1363,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1409,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592539</v>
+        <v>592379</v>
       </c>
       <c r="R8" t="n">
-        <v>7056491</v>
+        <v>7056750</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1454,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,7 +1466,7 @@
         <v>121147570</v>
       </c>
       <c r="B9" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1603,10 +1585,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121146548</v>
+        <v>121147583</v>
       </c>
       <c r="B10" t="n">
-        <v>79679</v>
+        <v>78601</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,21 +1601,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1643,10 +1625,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592514</v>
+        <v>592533</v>
       </c>
       <c r="R10" t="n">
-        <v>7056616</v>
+        <v>7056442</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,7 +1660,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1688,7 +1670,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,22 +1685,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121146507</v>
+        <v>121146532</v>
       </c>
       <c r="B11" t="n">
-        <v>57348</v>
+        <v>95375</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,43 +1709,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592490</v>
+        <v>592507</v>
       </c>
       <c r="R11" t="n">
-        <v>7056647</v>
+        <v>7056634</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,7 +1772,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1805,12 +1782,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,22 +1797,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121146852</v>
+        <v>121146485</v>
       </c>
       <c r="B12" t="n">
-        <v>57348</v>
+        <v>98081</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1849,31 +1821,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1882,10 +1853,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592599</v>
+        <v>592495</v>
       </c>
       <c r="R12" t="n">
-        <v>7056477</v>
+        <v>7056643</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1917,7 +1888,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1927,12 +1898,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1947,22 +1913,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121147630</v>
+        <v>121147489</v>
       </c>
       <c r="B13" t="n">
-        <v>79679</v>
+        <v>98081</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1971,38 +1937,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592484</v>
+        <v>592612</v>
       </c>
       <c r="R13" t="n">
-        <v>7056497</v>
+        <v>7056379</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2034,7 +2004,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2044,7 +2014,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2071,10 +2041,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121146641</v>
+        <v>121147630</v>
       </c>
       <c r="B14" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2087,21 +2057,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2111,10 +2081,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592519</v>
+        <v>592484</v>
       </c>
       <c r="R14" t="n">
-        <v>7056540</v>
+        <v>7056497</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2146,7 +2116,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2156,7 +2126,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2171,22 +2141,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121146572</v>
+        <v>121146483</v>
       </c>
       <c r="B15" t="n">
-        <v>91127</v>
+        <v>57351</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2195,38 +2165,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592530</v>
+        <v>592490</v>
       </c>
       <c r="R15" t="n">
-        <v>7056612</v>
+        <v>7056655</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2258,7 +2233,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2268,7 +2243,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2283,22 +2263,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121147410</v>
+        <v>121146592</v>
       </c>
       <c r="B16" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2330,7 +2310,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2339,10 +2319,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>592612</v>
+        <v>592533</v>
       </c>
       <c r="R16" t="n">
-        <v>7056401</v>
+        <v>7056596</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2374,7 +2354,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2384,7 +2364,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2411,10 +2391,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121147489</v>
+        <v>121146641</v>
       </c>
       <c r="B17" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2423,42 +2403,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>592612</v>
+        <v>592519</v>
       </c>
       <c r="R17" t="n">
-        <v>7056379</v>
+        <v>7056540</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2490,7 +2466,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2500,7 +2476,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2515,22 +2491,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121146590</v>
+        <v>121146852</v>
       </c>
       <c r="B18" t="n">
-        <v>90652</v>
+        <v>57351</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2539,38 +2515,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592518</v>
+        <v>592599</v>
       </c>
       <c r="R18" t="n">
-        <v>7056599</v>
+        <v>7056477</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2602,7 +2583,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2612,7 +2593,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2639,10 +2625,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121146679</v>
+        <v>121146590</v>
       </c>
       <c r="B19" t="n">
-        <v>90652</v>
+        <v>90662</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2679,10 +2665,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592516</v>
+        <v>592518</v>
       </c>
       <c r="R19" t="n">
-        <v>7056543</v>
+        <v>7056599</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2714,7 +2700,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2724,7 +2710,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2751,10 +2737,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121146496</v>
+        <v>121146704</v>
       </c>
       <c r="B20" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2767,21 +2753,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2791,10 +2777,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592472</v>
+        <v>592539</v>
       </c>
       <c r="R20" t="n">
-        <v>7056658</v>
+        <v>7056491</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2826,7 +2812,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2836,7 +2822,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2863,10 +2849,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121146532</v>
+        <v>121146496</v>
       </c>
       <c r="B21" t="n">
-        <v>95365</v>
+        <v>78601</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2875,25 +2861,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2903,10 +2889,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>592507</v>
+        <v>592472</v>
       </c>
       <c r="R21" t="n">
-        <v>7056634</v>
+        <v>7056658</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2938,7 +2924,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2948,7 +2934,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2975,10 +2961,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121146710</v>
+        <v>121146481</v>
       </c>
       <c r="B22" t="n">
-        <v>78598</v>
+        <v>98081</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2987,38 +2973,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>592531</v>
+        <v>592483</v>
       </c>
       <c r="R22" t="n">
-        <v>7056489</v>
+        <v>7056656</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3050,7 +3040,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3060,7 +3050,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3087,10 +3077,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121147437</v>
+        <v>121146507</v>
       </c>
       <c r="B23" t="n">
-        <v>57501</v>
+        <v>57351</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3103,31 +3093,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3136,13 +3122,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>592631</v>
+        <v>592490</v>
       </c>
       <c r="R23" t="n">
-        <v>7056396</v>
+        <v>7056647</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3171,7 +3157,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3181,7 +3167,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3196,22 +3187,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121146683</v>
+        <v>121146548</v>
       </c>
       <c r="B24" t="n">
-        <v>90705</v>
+        <v>79682</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3224,21 +3215,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3248,10 +3239,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592517</v>
+        <v>592514</v>
       </c>
       <c r="R24" t="n">
-        <v>7056543</v>
+        <v>7056616</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3283,7 +3274,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3293,7 +3284,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3320,10 +3311,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121146575</v>
+        <v>121147437</v>
       </c>
       <c r="B25" t="n">
-        <v>79679</v>
+        <v>57504</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3336,37 +3327,46 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>592529</v>
+        <v>592631</v>
       </c>
       <c r="R25" t="n">
-        <v>7056593</v>
+        <v>7056396</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3420,22 +3420,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121146272</v>
+        <v>121147479</v>
       </c>
       <c r="B26" t="n">
-        <v>79679</v>
+        <v>95375</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3444,25 +3444,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592457</v>
+        <v>592613</v>
       </c>
       <c r="R26" t="n">
-        <v>7056760</v>
+        <v>7056374</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3532,22 +3532,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121146481</v>
+        <v>121146569</v>
       </c>
       <c r="B27" t="n">
-        <v>98071</v>
+        <v>90983</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3556,42 +3556,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592483</v>
+        <v>592513</v>
       </c>
       <c r="R27" t="n">
-        <v>7056656</v>
+        <v>7056596</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3623,7 +3619,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3633,7 +3629,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3648,22 +3644,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121147431</v>
+        <v>121147410</v>
       </c>
       <c r="B28" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3695,7 +3691,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3704,10 +3700,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>592617</v>
+        <v>592612</v>
       </c>
       <c r="R28" t="n">
-        <v>7056397</v>
+        <v>7056401</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3739,7 +3735,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3749,7 +3745,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3776,10 +3772,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121147583</v>
+        <v>121146430</v>
       </c>
       <c r="B29" t="n">
-        <v>78598</v>
+        <v>98081</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3788,38 +3784,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>592533</v>
+        <v>592474</v>
       </c>
       <c r="R29" t="n">
-        <v>7056442</v>
+        <v>7056672</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3888,10 +3888,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121146339</v>
+        <v>121146683</v>
       </c>
       <c r="B30" t="n">
-        <v>91963</v>
+        <v>90715</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3900,25 +3900,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592379</v>
+        <v>592517</v>
       </c>
       <c r="R30" t="n">
-        <v>7056750</v>
+        <v>7056543</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3963,7 +3963,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 51337-2024 artfynd.xlsx
+++ b/artfynd/A 51337-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121146575</v>
+        <v>121146679</v>
       </c>
       <c r="B2" t="n">
-        <v>79682</v>
+        <v>90662</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592529</v>
+        <v>592516</v>
       </c>
       <c r="R2" t="n">
-        <v>7056593</v>
+        <v>7056543</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121146679</v>
+        <v>121146575</v>
       </c>
       <c r="B3" t="n">
-        <v>90662</v>
+        <v>79682</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592516</v>
+        <v>592529</v>
       </c>
       <c r="R3" t="n">
-        <v>7056543</v>
+        <v>7056593</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121147431</v>
+        <v>121146572</v>
       </c>
       <c r="B4" t="n">
-        <v>98081</v>
+        <v>91137</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,38 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592617</v>
+        <v>592530</v>
       </c>
       <c r="R4" t="n">
-        <v>7056397</v>
+        <v>7056612</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121146272</v>
+        <v>121147431</v>
       </c>
       <c r="B5" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,38 +1023,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592457</v>
+        <v>592617</v>
       </c>
       <c r="R5" t="n">
-        <v>7056760</v>
+        <v>7056397</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121146710</v>
+        <v>121146272</v>
       </c>
       <c r="B6" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,21 +1143,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592531</v>
+        <v>592457</v>
       </c>
       <c r="R6" t="n">
-        <v>7056489</v>
+        <v>7056760</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121146572</v>
+        <v>121146710</v>
       </c>
       <c r="B7" t="n">
-        <v>91137</v>
+        <v>78601</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,25 +1251,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592530</v>
+        <v>592531</v>
       </c>
       <c r="R7" t="n">
-        <v>7056612</v>
+        <v>7056489</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,12 +1339,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1585,10 +1585,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121147583</v>
+        <v>121146485</v>
       </c>
       <c r="B10" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,38 +1597,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592533</v>
+        <v>592495</v>
       </c>
       <c r="R10" t="n">
-        <v>7056442</v>
+        <v>7056643</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1660,7 +1664,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1670,7 +1674,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,10 +1701,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121146532</v>
+        <v>121147489</v>
       </c>
       <c r="B11" t="n">
-        <v>95375</v>
+        <v>98081</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,38 +1713,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592507</v>
+        <v>592612</v>
       </c>
       <c r="R11" t="n">
-        <v>7056634</v>
+        <v>7056379</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1772,7 +1780,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1782,7 +1790,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1797,22 +1805,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121146485</v>
+        <v>121146532</v>
       </c>
       <c r="B12" t="n">
-        <v>98081</v>
+        <v>95375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,42 +1829,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592495</v>
+        <v>592507</v>
       </c>
       <c r="R12" t="n">
-        <v>7056643</v>
+        <v>7056634</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1888,7 +1892,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1898,7 +1902,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1913,22 +1917,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121147489</v>
+        <v>121147583</v>
       </c>
       <c r="B13" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1937,42 +1941,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592612</v>
+        <v>592533</v>
       </c>
       <c r="R13" t="n">
-        <v>7056379</v>
+        <v>7056442</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 51337-2024 artfynd.xlsx
+++ b/artfynd/A 51337-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121146679</v>
+        <v>121146575</v>
       </c>
       <c r="B2" t="n">
-        <v>90662</v>
+        <v>79682</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592516</v>
+        <v>592529</v>
       </c>
       <c r="R2" t="n">
-        <v>7056543</v>
+        <v>7056593</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121146575</v>
+        <v>121146679</v>
       </c>
       <c r="B3" t="n">
-        <v>79682</v>
+        <v>90662</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592529</v>
+        <v>592516</v>
       </c>
       <c r="R3" t="n">
-        <v>7056593</v>
+        <v>7056543</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,12 +887,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 51337-2024 artfynd.xlsx
+++ b/artfynd/A 51337-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121146575</v>
+        <v>121147583</v>
       </c>
       <c r="B2" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592529</v>
+        <v>592533</v>
       </c>
       <c r="R2" t="n">
-        <v>7056593</v>
+        <v>7056442</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121146679</v>
+        <v>121146569</v>
       </c>
       <c r="B3" t="n">
-        <v>90662</v>
+        <v>90983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592516</v>
+        <v>592513</v>
       </c>
       <c r="R3" t="n">
-        <v>7056543</v>
+        <v>7056596</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121146572</v>
+        <v>121146679</v>
       </c>
       <c r="B4" t="n">
-        <v>91137</v>
+        <v>90662</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592530</v>
+        <v>592516</v>
       </c>
       <c r="R4" t="n">
-        <v>7056612</v>
+        <v>7056543</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121147431</v>
+        <v>121146548</v>
       </c>
       <c r="B5" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,42 +1023,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592617</v>
+        <v>592514</v>
       </c>
       <c r="R5" t="n">
-        <v>7056397</v>
+        <v>7056616</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,22 +1111,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121146272</v>
+        <v>121146483</v>
       </c>
       <c r="B6" t="n">
-        <v>79682</v>
+        <v>57351</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,34 +1139,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592457</v>
+        <v>592490</v>
       </c>
       <c r="R6" t="n">
-        <v>7056760</v>
+        <v>7056655</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1213,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121146710</v>
+        <v>121147479</v>
       </c>
       <c r="B7" t="n">
-        <v>78601</v>
+        <v>95375</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,25 +1257,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592531</v>
+        <v>592613</v>
       </c>
       <c r="R7" t="n">
-        <v>7056489</v>
+        <v>7056374</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,22 +1345,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121146339</v>
+        <v>121146572</v>
       </c>
       <c r="B8" t="n">
-        <v>91973</v>
+        <v>91137</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,25 +1369,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592379</v>
+        <v>592530</v>
       </c>
       <c r="R8" t="n">
-        <v>7056750</v>
+        <v>7056612</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121147570</v>
+        <v>121146339</v>
       </c>
       <c r="B9" t="n">
-        <v>57351</v>
+        <v>91973</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,43 +1481,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592521</v>
+        <v>592379</v>
       </c>
       <c r="R9" t="n">
-        <v>7056445</v>
+        <v>7056750</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1543,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1553,12 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121146485</v>
+        <v>121146532</v>
       </c>
       <c r="B10" t="n">
-        <v>98081</v>
+        <v>95375</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,42 +1593,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592495</v>
+        <v>592507</v>
       </c>
       <c r="R10" t="n">
-        <v>7056643</v>
+        <v>7056634</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1674,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,22 +1681,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121147489</v>
+        <v>121146852</v>
       </c>
       <c r="B11" t="n">
-        <v>98081</v>
+        <v>57351</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1713,30 +1705,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1745,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592612</v>
+        <v>592599</v>
       </c>
       <c r="R11" t="n">
-        <v>7056379</v>
+        <v>7056477</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1780,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1790,7 +1783,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,22 +1803,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121146532</v>
+        <v>121146683</v>
       </c>
       <c r="B12" t="n">
-        <v>95375</v>
+        <v>90715</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,25 +1827,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2869</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1857,10 +1855,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592507</v>
+        <v>592517</v>
       </c>
       <c r="R12" t="n">
-        <v>7056634</v>
+        <v>7056543</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1892,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1902,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,7 +1927,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121147583</v>
+        <v>121146496</v>
       </c>
       <c r="B13" t="n">
         <v>78601</v>
@@ -1969,10 +1967,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592533</v>
+        <v>592472</v>
       </c>
       <c r="R13" t="n">
-        <v>7056442</v>
+        <v>7056658</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2004,7 +2002,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2014,7 +2012,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,19 +2027,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121147630</v>
+        <v>121146704</v>
       </c>
       <c r="B14" t="n">
         <v>79682</v>
@@ -2081,10 +2079,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592484</v>
+        <v>592539</v>
       </c>
       <c r="R14" t="n">
-        <v>7056497</v>
+        <v>7056491</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2116,7 +2114,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2126,7 +2124,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,22 +2139,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121146483</v>
+        <v>121147489</v>
       </c>
       <c r="B15" t="n">
-        <v>57351</v>
+        <v>98081</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2165,31 +2163,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2198,10 +2195,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592490</v>
+        <v>592612</v>
       </c>
       <c r="R15" t="n">
-        <v>7056655</v>
+        <v>7056379</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2233,7 +2230,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2243,12 +2240,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:41</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2275,10 +2267,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121146592</v>
+        <v>121146575</v>
       </c>
       <c r="B16" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2287,42 +2279,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>592533</v>
+        <v>592529</v>
       </c>
       <c r="R16" t="n">
-        <v>7056596</v>
+        <v>7056593</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2354,7 +2342,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2364,7 +2352,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2391,10 +2379,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121146641</v>
+        <v>121147570</v>
       </c>
       <c r="B17" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2407,34 +2395,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>592519</v>
+        <v>592521</v>
       </c>
       <c r="R17" t="n">
-        <v>7056540</v>
+        <v>7056445</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2466,7 +2459,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2476,7 +2469,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2503,10 +2501,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121146852</v>
+        <v>121146710</v>
       </c>
       <c r="B18" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2519,39 +2517,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592599</v>
+        <v>592531</v>
       </c>
       <c r="R18" t="n">
-        <v>7056477</v>
+        <v>7056489</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2583,7 +2576,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2593,12 +2586,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2613,22 +2601,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121146590</v>
+        <v>121146641</v>
       </c>
       <c r="B19" t="n">
-        <v>90662</v>
+        <v>78601</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2637,25 +2625,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2665,10 +2653,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592518</v>
+        <v>592519</v>
       </c>
       <c r="R19" t="n">
-        <v>7056599</v>
+        <v>7056540</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2700,7 +2688,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2710,7 +2698,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2737,10 +2725,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121146704</v>
+        <v>121146507</v>
       </c>
       <c r="B20" t="n">
-        <v>79682</v>
+        <v>57351</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2753,34 +2741,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592539</v>
+        <v>592490</v>
       </c>
       <c r="R20" t="n">
-        <v>7056491</v>
+        <v>7056647</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2812,7 +2805,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2822,7 +2815,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2837,22 +2835,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121146496</v>
+        <v>121146272</v>
       </c>
       <c r="B21" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2865,21 +2863,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2889,10 +2887,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>592472</v>
+        <v>592457</v>
       </c>
       <c r="R21" t="n">
-        <v>7056658</v>
+        <v>7056760</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2924,7 +2922,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2934,7 +2932,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2949,22 +2947,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121146481</v>
+        <v>121147437</v>
       </c>
       <c r="B22" t="n">
-        <v>98081</v>
+        <v>57504</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2973,30 +2971,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3005,13 +3008,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>592483</v>
+        <v>592631</v>
       </c>
       <c r="R22" t="n">
-        <v>7056656</v>
+        <v>7056396</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3040,7 +3043,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3050,7 +3053,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3065,22 +3068,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121146507</v>
+        <v>121146485</v>
       </c>
       <c r="B23" t="n">
-        <v>57351</v>
+        <v>98081</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3089,31 +3092,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3122,10 +3124,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>592490</v>
+        <v>592495</v>
       </c>
       <c r="R23" t="n">
-        <v>7056647</v>
+        <v>7056643</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3157,7 +3159,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3167,12 +3169,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3199,10 +3196,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121146548</v>
+        <v>121147410</v>
       </c>
       <c r="B24" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3211,38 +3208,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592514</v>
+        <v>592612</v>
       </c>
       <c r="R24" t="n">
-        <v>7056616</v>
+        <v>7056401</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3274,7 +3275,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3284,7 +3285,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3299,22 +3300,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121147437</v>
+        <v>121146590</v>
       </c>
       <c r="B25" t="n">
-        <v>57504</v>
+        <v>90662</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3323,50 +3324,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>592631</v>
+        <v>592518</v>
       </c>
       <c r="R25" t="n">
-        <v>7056396</v>
+        <v>7056599</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3395,7 +3387,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3405,7 +3397,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3432,10 +3424,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121147479</v>
+        <v>121146430</v>
       </c>
       <c r="B26" t="n">
-        <v>95375</v>
+        <v>98081</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3444,38 +3436,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592613</v>
+        <v>592474</v>
       </c>
       <c r="R26" t="n">
-        <v>7056374</v>
+        <v>7056672</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3507,7 +3503,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3517,7 +3513,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3532,22 +3528,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121146569</v>
+        <v>121147630</v>
       </c>
       <c r="B27" t="n">
-        <v>90983</v>
+        <v>79682</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3560,21 +3556,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3584,10 +3580,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592513</v>
+        <v>592484</v>
       </c>
       <c r="R27" t="n">
-        <v>7056596</v>
+        <v>7056497</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3619,7 +3615,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3629,7 +3625,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3644,19 +3640,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121147410</v>
+        <v>121146592</v>
       </c>
       <c r="B28" t="n">
         <v>98081</v>
@@ -3691,7 +3687,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3700,10 +3696,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>592612</v>
+        <v>592533</v>
       </c>
       <c r="R28" t="n">
-        <v>7056401</v>
+        <v>7056596</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3735,7 +3731,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3745,7 +3741,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3772,7 +3768,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121146430</v>
+        <v>121147431</v>
       </c>
       <c r="B29" t="n">
         <v>98081</v>
@@ -3807,7 +3803,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3816,10 +3812,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>592474</v>
+        <v>592617</v>
       </c>
       <c r="R29" t="n">
-        <v>7056672</v>
+        <v>7056397</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3851,7 +3847,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3861,7 +3857,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3888,10 +3884,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121146683</v>
+        <v>121146481</v>
       </c>
       <c r="B30" t="n">
-        <v>90715</v>
+        <v>98081</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3900,38 +3896,42 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592517</v>
+        <v>592483</v>
       </c>
       <c r="R30" t="n">
-        <v>7056543</v>
+        <v>7056656</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3963,7 +3963,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3988,12 +3988,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>

--- a/artfynd/A 51337-2024 artfynd.xlsx
+++ b/artfynd/A 51337-2024 artfynd.xlsx
@@ -1693,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121146852</v>
+        <v>121146704</v>
       </c>
       <c r="B11" t="n">
-        <v>57351</v>
+        <v>79682</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,39 +1709,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592599</v>
+        <v>592539</v>
       </c>
       <c r="R11" t="n">
-        <v>7056477</v>
+        <v>7056491</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1773,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,12 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2039,10 +2029,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121146704</v>
+        <v>121146852</v>
       </c>
       <c r="B14" t="n">
-        <v>79682</v>
+        <v>57351</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2055,34 +2045,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592539</v>
+        <v>592599</v>
       </c>
       <c r="R14" t="n">
-        <v>7056491</v>
+        <v>7056477</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2114,7 +2109,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2124,7 +2119,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 51337-2024 artfynd.xlsx
+++ b/artfynd/A 51337-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121147583</v>
+        <v>121146590</v>
       </c>
       <c r="B2" t="n">
-        <v>78601</v>
+        <v>90674</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592533</v>
+        <v>592518</v>
       </c>
       <c r="R2" t="n">
-        <v>7056442</v>
+        <v>7056599</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121146569</v>
+        <v>121146683</v>
       </c>
       <c r="B3" t="n">
-        <v>90983</v>
+        <v>90727</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592513</v>
+        <v>592517</v>
       </c>
       <c r="R3" t="n">
-        <v>7056596</v>
+        <v>7056543</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121146679</v>
+        <v>121147570</v>
       </c>
       <c r="B4" t="n">
-        <v>90662</v>
+        <v>57351</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,38 +911,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592516</v>
+        <v>592521</v>
       </c>
       <c r="R4" t="n">
-        <v>7056543</v>
+        <v>7056445</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121146548</v>
+        <v>121147437</v>
       </c>
       <c r="B5" t="n">
-        <v>79682</v>
+        <v>57504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,37 +1037,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592514</v>
+        <v>592631</v>
       </c>
       <c r="R5" t="n">
-        <v>7056616</v>
+        <v>7056396</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121146483</v>
+        <v>121146485</v>
       </c>
       <c r="B6" t="n">
-        <v>57351</v>
+        <v>98094</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,31 +1154,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1168,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592490</v>
+        <v>592495</v>
       </c>
       <c r="R6" t="n">
-        <v>7056655</v>
+        <v>7056643</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,12 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:41</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121147479</v>
+        <v>121147431</v>
       </c>
       <c r="B7" t="n">
-        <v>95375</v>
+        <v>98094</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,38 +1270,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592613</v>
+        <v>592617</v>
       </c>
       <c r="R7" t="n">
-        <v>7056374</v>
+        <v>7056397</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1337,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1347,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,22 +1362,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121146572</v>
+        <v>121146548</v>
       </c>
       <c r="B8" t="n">
-        <v>91137</v>
+        <v>79685</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,25 +1386,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592530</v>
+        <v>592514</v>
       </c>
       <c r="R8" t="n">
-        <v>7056612</v>
+        <v>7056616</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,7 +1449,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1459,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121146339</v>
+        <v>121146532</v>
       </c>
       <c r="B9" t="n">
-        <v>91973</v>
+        <v>95388</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,21 +1502,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1509,10 +1526,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592379</v>
+        <v>592507</v>
       </c>
       <c r="R9" t="n">
-        <v>7056750</v>
+        <v>7056634</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121146532</v>
+        <v>121146592</v>
       </c>
       <c r="B10" t="n">
-        <v>95375</v>
+        <v>98094</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,38 +1610,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592507</v>
+        <v>592533</v>
       </c>
       <c r="R10" t="n">
-        <v>7056634</v>
+        <v>7056596</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,7 +1677,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1687,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1681,22 +1702,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121146704</v>
+        <v>121147630</v>
       </c>
       <c r="B11" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1733,10 +1754,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592539</v>
+        <v>592484</v>
       </c>
       <c r="R11" t="n">
-        <v>7056491</v>
+        <v>7056497</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1768,7 +1789,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1799,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1793,22 +1814,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121146683</v>
+        <v>121147410</v>
       </c>
       <c r="B12" t="n">
-        <v>90715</v>
+        <v>98094</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1817,38 +1838,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592517</v>
+        <v>592612</v>
       </c>
       <c r="R12" t="n">
-        <v>7056543</v>
+        <v>7056401</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1880,7 +1905,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1915,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1905,22 +1930,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121146496</v>
+        <v>121146679</v>
       </c>
       <c r="B13" t="n">
-        <v>78601</v>
+        <v>90674</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1929,25 +1954,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1957,10 +1982,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592472</v>
+        <v>592516</v>
       </c>
       <c r="R13" t="n">
-        <v>7056658</v>
+        <v>7056543</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1992,7 +2017,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +2027,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,10 +2054,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121146852</v>
+        <v>121146704</v>
       </c>
       <c r="B14" t="n">
-        <v>57351</v>
+        <v>79685</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2045,39 +2070,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592599</v>
+        <v>592539</v>
       </c>
       <c r="R14" t="n">
-        <v>7056477</v>
+        <v>7056491</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2109,7 +2129,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2119,12 +2139,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2151,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121147489</v>
+        <v>121146272</v>
       </c>
       <c r="B15" t="n">
-        <v>98081</v>
+        <v>79685</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2163,42 +2178,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592612</v>
+        <v>592457</v>
       </c>
       <c r="R15" t="n">
-        <v>7056379</v>
+        <v>7056760</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2230,7 +2241,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2240,7 +2251,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2267,10 +2278,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121146575</v>
+        <v>121147479</v>
       </c>
       <c r="B16" t="n">
-        <v>79682</v>
+        <v>95388</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2279,25 +2290,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2307,10 +2318,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>592529</v>
+        <v>592613</v>
       </c>
       <c r="R16" t="n">
-        <v>7056593</v>
+        <v>7056374</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2342,7 +2353,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2352,7 +2363,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2367,19 +2378,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121147570</v>
+        <v>121146507</v>
       </c>
       <c r="B17" t="n">
         <v>57351</v>
@@ -2424,10 +2435,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>592521</v>
+        <v>592490</v>
       </c>
       <c r="R17" t="n">
-        <v>7056445</v>
+        <v>7056647</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2459,7 +2470,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2469,12 +2480,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2489,22 +2500,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121146710</v>
+        <v>121146496</v>
       </c>
       <c r="B18" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2541,10 +2552,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592531</v>
+        <v>592472</v>
       </c>
       <c r="R18" t="n">
-        <v>7056489</v>
+        <v>7056658</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2576,7 +2587,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2586,7 +2597,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2601,22 +2612,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121146641</v>
+        <v>121146430</v>
       </c>
       <c r="B19" t="n">
-        <v>78601</v>
+        <v>98094</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2625,38 +2636,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592519</v>
+        <v>592474</v>
       </c>
       <c r="R19" t="n">
-        <v>7056540</v>
+        <v>7056672</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2688,7 +2703,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2698,7 +2713,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2713,22 +2728,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121146507</v>
+        <v>121146575</v>
       </c>
       <c r="B20" t="n">
-        <v>57351</v>
+        <v>79685</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2741,39 +2756,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592490</v>
+        <v>592529</v>
       </c>
       <c r="R20" t="n">
-        <v>7056647</v>
+        <v>7056593</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2805,7 +2815,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2815,12 +2825,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2847,10 +2852,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121146272</v>
+        <v>121146710</v>
       </c>
       <c r="B21" t="n">
-        <v>79682</v>
+        <v>78604</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2863,21 +2868,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2887,10 +2892,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>592457</v>
+        <v>592531</v>
       </c>
       <c r="R21" t="n">
-        <v>7056760</v>
+        <v>7056489</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2922,7 +2927,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2932,7 +2937,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2959,10 +2964,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121147437</v>
+        <v>121147583</v>
       </c>
       <c r="B22" t="n">
-        <v>57504</v>
+        <v>78604</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2975,46 +2980,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>592631</v>
+        <v>592533</v>
       </c>
       <c r="R22" t="n">
-        <v>7056396</v>
+        <v>7056442</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3043,7 +3039,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3053,7 +3049,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3068,22 +3064,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121146485</v>
+        <v>121146569</v>
       </c>
       <c r="B23" t="n">
-        <v>98081</v>
+        <v>90995</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3092,42 +3088,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>592495</v>
+        <v>592513</v>
       </c>
       <c r="R23" t="n">
-        <v>7056643</v>
+        <v>7056596</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3159,7 +3151,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3169,7 +3161,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3184,22 +3176,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121147410</v>
+        <v>121146641</v>
       </c>
       <c r="B24" t="n">
-        <v>98081</v>
+        <v>78604</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3208,42 +3200,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592612</v>
+        <v>592519</v>
       </c>
       <c r="R24" t="n">
-        <v>7056401</v>
+        <v>7056540</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3275,7 +3263,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3285,7 +3273,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3300,22 +3288,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121146590</v>
+        <v>121146481</v>
       </c>
       <c r="B25" t="n">
-        <v>90662</v>
+        <v>98094</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3324,38 +3312,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>592518</v>
+        <v>592483</v>
       </c>
       <c r="R25" t="n">
-        <v>7056599</v>
+        <v>7056656</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3387,7 +3379,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3397,7 +3389,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3412,22 +3404,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121146430</v>
+        <v>121147489</v>
       </c>
       <c r="B26" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3459,7 +3451,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3468,10 +3460,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592474</v>
+        <v>592612</v>
       </c>
       <c r="R26" t="n">
-        <v>7056672</v>
+        <v>7056379</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3503,7 +3495,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3513,7 +3505,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3540,10 +3532,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121147630</v>
+        <v>121146339</v>
       </c>
       <c r="B27" t="n">
-        <v>79682</v>
+        <v>91985</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3552,25 +3544,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3580,10 +3572,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592484</v>
+        <v>592379</v>
       </c>
       <c r="R27" t="n">
-        <v>7056497</v>
+        <v>7056750</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3615,7 +3607,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3625,7 +3617,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3640,22 +3632,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121146592</v>
+        <v>121146483</v>
       </c>
       <c r="B28" t="n">
-        <v>98081</v>
+        <v>57351</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3664,30 +3656,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3696,10 +3689,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>592533</v>
+        <v>592490</v>
       </c>
       <c r="R28" t="n">
-        <v>7056596</v>
+        <v>7056655</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3731,7 +3724,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3741,7 +3734,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3768,10 +3766,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121147431</v>
+        <v>121146852</v>
       </c>
       <c r="B29" t="n">
-        <v>98081</v>
+        <v>57351</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3780,30 +3778,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3812,10 +3811,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>592617</v>
+        <v>592599</v>
       </c>
       <c r="R29" t="n">
-        <v>7056397</v>
+        <v>7056477</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3847,7 +3846,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3857,7 +3856,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3872,22 +3876,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121146481</v>
+        <v>121146572</v>
       </c>
       <c r="B30" t="n">
-        <v>98081</v>
+        <v>91149</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3900,38 +3904,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592483</v>
+        <v>592530</v>
       </c>
       <c r="R30" t="n">
-        <v>7056656</v>
+        <v>7056612</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3963,7 +3963,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3988,12 +3988,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>

--- a/artfynd/A 51337-2024 artfynd.xlsx
+++ b/artfynd/A 51337-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121146590</v>
+        <v>121146481</v>
       </c>
       <c r="B2" t="n">
-        <v>90674</v>
+        <v>98095</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592518</v>
+        <v>592483</v>
       </c>
       <c r="R2" t="n">
-        <v>7056599</v>
+        <v>7056656</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +779,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121146683</v>
+        <v>121147479</v>
       </c>
       <c r="B3" t="n">
-        <v>90727</v>
+        <v>95389</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>2869</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592517</v>
+        <v>592613</v>
       </c>
       <c r="R3" t="n">
-        <v>7056543</v>
+        <v>7056374</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121147570</v>
+        <v>121146710</v>
       </c>
       <c r="B4" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +919,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592521</v>
+        <v>592531</v>
       </c>
       <c r="R4" t="n">
-        <v>7056445</v>
+        <v>7056489</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,22 +1003,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121147437</v>
+        <v>121146683</v>
       </c>
       <c r="B5" t="n">
-        <v>57504</v>
+        <v>90728</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,46 +1031,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592631</v>
+        <v>592517</v>
       </c>
       <c r="R5" t="n">
-        <v>7056396</v>
+        <v>7056543</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121146485</v>
+        <v>121146592</v>
       </c>
       <c r="B6" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1186,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592495</v>
+        <v>592533</v>
       </c>
       <c r="R6" t="n">
-        <v>7056643</v>
+        <v>7056596</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,7 +1206,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1216,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,10 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121147431</v>
+        <v>121147489</v>
       </c>
       <c r="B7" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1293,7 +1278,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1302,10 +1287,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592617</v>
+        <v>592612</v>
       </c>
       <c r="R7" t="n">
-        <v>7056397</v>
+        <v>7056379</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,7 +1332,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121146548</v>
+        <v>121146485</v>
       </c>
       <c r="B8" t="n">
-        <v>79685</v>
+        <v>98095</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,38 +1371,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592514</v>
+        <v>592495</v>
       </c>
       <c r="R8" t="n">
-        <v>7056616</v>
+        <v>7056643</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1449,7 +1438,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1459,7 +1448,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,22 +1463,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121146532</v>
+        <v>121146483</v>
       </c>
       <c r="B9" t="n">
-        <v>95388</v>
+        <v>57351</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,38 +1487,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592507</v>
+        <v>592490</v>
       </c>
       <c r="R9" t="n">
-        <v>7056634</v>
+        <v>7056655</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1561,7 +1555,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,7 +1565,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,22 +1585,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121146592</v>
+        <v>121147583</v>
       </c>
       <c r="B10" t="n">
-        <v>98094</v>
+        <v>78604</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,32 +1609,28 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
@@ -1645,7 +1640,7 @@
         <v>592533</v>
       </c>
       <c r="R10" t="n">
-        <v>7056596</v>
+        <v>7056442</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1672,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1687,7 +1682,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1714,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121147630</v>
+        <v>121146339</v>
       </c>
       <c r="B11" t="n">
-        <v>79685</v>
+        <v>91986</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1726,25 +1721,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1754,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592484</v>
+        <v>592379</v>
       </c>
       <c r="R11" t="n">
-        <v>7056497</v>
+        <v>7056750</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,7 +1784,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1799,7 +1794,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,22 +1809,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121147410</v>
+        <v>121147431</v>
       </c>
       <c r="B12" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1861,7 +1856,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1870,10 +1865,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592612</v>
+        <v>592617</v>
       </c>
       <c r="R12" t="n">
-        <v>7056401</v>
+        <v>7056397</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1915,7 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1942,10 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121146679</v>
+        <v>121146572</v>
       </c>
       <c r="B13" t="n">
-        <v>90674</v>
+        <v>91150</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1954,25 +1949,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1982,10 +1977,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592516</v>
+        <v>592530</v>
       </c>
       <c r="R13" t="n">
-        <v>7056543</v>
+        <v>7056612</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2017,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2027,7 +2022,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2054,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121146704</v>
+        <v>121146569</v>
       </c>
       <c r="B14" t="n">
-        <v>79685</v>
+        <v>90996</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2070,21 +2065,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2094,10 +2089,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592539</v>
+        <v>592513</v>
       </c>
       <c r="R14" t="n">
-        <v>7056491</v>
+        <v>7056596</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,7 +2124,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,7 +2134,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2166,10 +2161,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121146272</v>
+        <v>121146641</v>
       </c>
       <c r="B15" t="n">
-        <v>79685</v>
+        <v>78604</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2182,21 +2177,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2206,10 +2201,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592457</v>
+        <v>592519</v>
       </c>
       <c r="R15" t="n">
-        <v>7056760</v>
+        <v>7056540</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2241,7 +2236,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2251,7 +2246,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2266,22 +2261,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121147479</v>
+        <v>121146704</v>
       </c>
       <c r="B16" t="n">
-        <v>95388</v>
+        <v>79685</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2290,25 +2285,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2318,10 +2313,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>592613</v>
+        <v>592539</v>
       </c>
       <c r="R16" t="n">
-        <v>7056374</v>
+        <v>7056491</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2353,7 +2348,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2363,7 +2358,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2390,10 +2385,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121146507</v>
+        <v>121146532</v>
       </c>
       <c r="B17" t="n">
-        <v>57351</v>
+        <v>95389</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2402,43 +2397,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>592490</v>
+        <v>592507</v>
       </c>
       <c r="R17" t="n">
-        <v>7056647</v>
+        <v>7056634</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2470,7 +2460,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2480,12 +2470,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,22 +2485,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121146496</v>
+        <v>121147410</v>
       </c>
       <c r="B18" t="n">
-        <v>78604</v>
+        <v>98095</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2524,38 +2509,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592472</v>
+        <v>592612</v>
       </c>
       <c r="R18" t="n">
-        <v>7056658</v>
+        <v>7056401</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2587,7 +2576,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2597,7 +2586,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2612,22 +2601,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121146430</v>
+        <v>121146590</v>
       </c>
       <c r="B19" t="n">
-        <v>98094</v>
+        <v>90675</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2636,42 +2625,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592474</v>
+        <v>592518</v>
       </c>
       <c r="R19" t="n">
-        <v>7056672</v>
+        <v>7056599</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2703,7 +2688,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2713,7 +2698,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2728,19 +2713,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121146575</v>
+        <v>121147630</v>
       </c>
       <c r="B20" t="n">
         <v>79685</v>
@@ -2780,10 +2765,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592529</v>
+        <v>592484</v>
       </c>
       <c r="R20" t="n">
-        <v>7056593</v>
+        <v>7056497</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2815,7 +2800,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2825,7 +2810,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2852,10 +2837,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121146710</v>
+        <v>121146575</v>
       </c>
       <c r="B21" t="n">
-        <v>78604</v>
+        <v>79685</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2868,21 +2853,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2892,10 +2877,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>592531</v>
+        <v>592529</v>
       </c>
       <c r="R21" t="n">
-        <v>7056489</v>
+        <v>7056593</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2927,7 +2912,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2937,7 +2922,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2964,10 +2949,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121147583</v>
+        <v>121146548</v>
       </c>
       <c r="B22" t="n">
-        <v>78604</v>
+        <v>79685</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2980,21 +2965,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3004,10 +2989,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>592533</v>
+        <v>592514</v>
       </c>
       <c r="R22" t="n">
-        <v>7056442</v>
+        <v>7056616</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3039,7 +3024,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3049,7 +3034,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3064,22 +3049,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121146569</v>
+        <v>121146272</v>
       </c>
       <c r="B23" t="n">
-        <v>90995</v>
+        <v>79685</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3092,21 +3077,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3116,10 +3101,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>592513</v>
+        <v>592457</v>
       </c>
       <c r="R23" t="n">
-        <v>7056596</v>
+        <v>7056760</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3151,7 +3136,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3161,7 +3146,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3176,22 +3161,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121146641</v>
+        <v>121146679</v>
       </c>
       <c r="B24" t="n">
-        <v>78604</v>
+        <v>90675</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3200,25 +3185,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3228,10 +3213,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592519</v>
+        <v>592516</v>
       </c>
       <c r="R24" t="n">
-        <v>7056540</v>
+        <v>7056543</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3263,7 +3248,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3273,7 +3258,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3300,10 +3285,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121146481</v>
+        <v>121147570</v>
       </c>
       <c r="B25" t="n">
-        <v>98094</v>
+        <v>57351</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3312,30 +3297,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3344,10 +3330,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>592483</v>
+        <v>592521</v>
       </c>
       <c r="R25" t="n">
-        <v>7056656</v>
+        <v>7056445</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3379,7 +3365,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3389,7 +3375,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3404,22 +3395,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121147489</v>
+        <v>121146852</v>
       </c>
       <c r="B26" t="n">
-        <v>98094</v>
+        <v>57351</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3428,30 +3419,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3460,10 +3452,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592612</v>
+        <v>592599</v>
       </c>
       <c r="R26" t="n">
-        <v>7056379</v>
+        <v>7056477</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3495,7 +3487,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3505,7 +3497,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3520,22 +3517,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121146339</v>
+        <v>121147437</v>
       </c>
       <c r="B27" t="n">
-        <v>91985</v>
+        <v>57504</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3544,41 +3541,50 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592379</v>
+        <v>592631</v>
       </c>
       <c r="R27" t="n">
-        <v>7056750</v>
+        <v>7056396</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3607,7 +3613,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3617,7 +3623,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3644,10 +3650,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121146483</v>
+        <v>121146430</v>
       </c>
       <c r="B28" t="n">
-        <v>57351</v>
+        <v>98095</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3656,31 +3662,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3689,10 +3694,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>592490</v>
+        <v>592474</v>
       </c>
       <c r="R28" t="n">
-        <v>7056655</v>
+        <v>7056672</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3724,7 +3729,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3734,12 +3739,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:41</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3766,10 +3766,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121146852</v>
+        <v>121146496</v>
       </c>
       <c r="B29" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3782,39 +3782,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>592599</v>
+        <v>592472</v>
       </c>
       <c r="R29" t="n">
-        <v>7056477</v>
+        <v>7056658</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3846,7 +3841,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3856,12 +3851,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3888,10 +3878,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121146572</v>
+        <v>121146507</v>
       </c>
       <c r="B30" t="n">
-        <v>91149</v>
+        <v>57351</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3900,38 +3890,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592530</v>
+        <v>592490</v>
       </c>
       <c r="R30" t="n">
-        <v>7056612</v>
+        <v>7056647</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3963,7 +3958,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3973,7 +3968,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3988,12 +3988,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>

--- a/artfynd/A 51337-2024 artfynd.xlsx
+++ b/artfynd/A 51337-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121146481</v>
+        <v>121147437</v>
       </c>
       <c r="B2" t="n">
-        <v>98095</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592483</v>
+        <v>592631</v>
       </c>
       <c r="R2" t="n">
-        <v>7056656</v>
+        <v>7056396</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,22 +784,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121147479</v>
+        <v>121146532</v>
       </c>
       <c r="B3" t="n">
-        <v>95389</v>
+        <v>95392</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -831,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592613</v>
+        <v>592507</v>
       </c>
       <c r="R3" t="n">
-        <v>7056374</v>
+        <v>7056634</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121146710</v>
+        <v>121146272</v>
       </c>
       <c r="B4" t="n">
-        <v>78604</v>
+        <v>79688</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +924,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592531</v>
+        <v>592457</v>
       </c>
       <c r="R4" t="n">
-        <v>7056489</v>
+        <v>7056760</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121146683</v>
+        <v>121146430</v>
       </c>
       <c r="B5" t="n">
-        <v>90728</v>
+        <v>98098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,38 +1032,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592517</v>
+        <v>592474</v>
       </c>
       <c r="R5" t="n">
-        <v>7056543</v>
+        <v>7056672</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,22 +1124,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121146592</v>
+        <v>121147630</v>
       </c>
       <c r="B6" t="n">
-        <v>98095</v>
+        <v>79688</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,42 +1148,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592533</v>
+        <v>592484</v>
       </c>
       <c r="R6" t="n">
-        <v>7056596</v>
+        <v>7056497</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1216,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121147489</v>
+        <v>121146507</v>
       </c>
       <c r="B7" t="n">
-        <v>98095</v>
+        <v>57354</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,30 +1260,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1287,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592612</v>
+        <v>592490</v>
       </c>
       <c r="R7" t="n">
-        <v>7056379</v>
+        <v>7056647</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1338,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121146485</v>
+        <v>121146481</v>
       </c>
       <c r="B8" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,7 +1405,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1403,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592495</v>
+        <v>592483</v>
       </c>
       <c r="R8" t="n">
-        <v>7056643</v>
+        <v>7056656</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,7 +1449,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1448,7 +1459,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,10 +1486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121146483</v>
+        <v>121146339</v>
       </c>
       <c r="B9" t="n">
-        <v>57351</v>
+        <v>91989</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,43 +1498,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592490</v>
+        <v>592379</v>
       </c>
       <c r="R9" t="n">
-        <v>7056655</v>
+        <v>7056750</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1565,12 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:41</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,22 +1586,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121147583</v>
+        <v>121147570</v>
       </c>
       <c r="B10" t="n">
-        <v>78604</v>
+        <v>57354</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1613,34 +1614,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592533</v>
+        <v>592521</v>
       </c>
       <c r="R10" t="n">
-        <v>7056442</v>
+        <v>7056445</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1672,7 +1678,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1682,7 +1688,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,22 +1708,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121146339</v>
+        <v>121146683</v>
       </c>
       <c r="B11" t="n">
-        <v>91986</v>
+        <v>90731</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,25 +1732,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1749,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592379</v>
+        <v>592517</v>
       </c>
       <c r="R11" t="n">
-        <v>7056750</v>
+        <v>7056543</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,7 +1795,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1794,7 +1805,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1821,10 +1832,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121147431</v>
+        <v>121146575</v>
       </c>
       <c r="B12" t="n">
-        <v>98095</v>
+        <v>79688</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1833,42 +1844,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592617</v>
+        <v>592529</v>
       </c>
       <c r="R12" t="n">
-        <v>7056397</v>
+        <v>7056593</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,7 +1907,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1917,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1937,10 +1944,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121146572</v>
+        <v>121146704</v>
       </c>
       <c r="B13" t="n">
-        <v>91150</v>
+        <v>79688</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1949,25 +1956,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1977,10 +1984,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592530</v>
+        <v>592539</v>
       </c>
       <c r="R13" t="n">
-        <v>7056612</v>
+        <v>7056491</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,7 +2019,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,7 +2029,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,10 +2056,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121146569</v>
+        <v>121146496</v>
       </c>
       <c r="B14" t="n">
-        <v>90996</v>
+        <v>78607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2065,21 +2072,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2089,10 +2096,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592513</v>
+        <v>592472</v>
       </c>
       <c r="R14" t="n">
-        <v>7056596</v>
+        <v>7056658</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,7 +2131,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2134,7 +2141,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2161,10 +2168,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121146641</v>
+        <v>121146590</v>
       </c>
       <c r="B15" t="n">
-        <v>78604</v>
+        <v>90678</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2173,25 +2180,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2201,10 +2208,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592519</v>
+        <v>592518</v>
       </c>
       <c r="R15" t="n">
-        <v>7056540</v>
+        <v>7056599</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,7 +2243,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2246,7 +2253,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2273,10 +2280,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121146704</v>
+        <v>121146548</v>
       </c>
       <c r="B16" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2313,10 +2320,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>592539</v>
+        <v>592514</v>
       </c>
       <c r="R16" t="n">
-        <v>7056491</v>
+        <v>7056616</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2348,7 +2355,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2358,7 +2365,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2385,10 +2392,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121146532</v>
+        <v>121147431</v>
       </c>
       <c r="B17" t="n">
-        <v>95389</v>
+        <v>98098</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2397,38 +2404,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>592507</v>
+        <v>592617</v>
       </c>
       <c r="R17" t="n">
-        <v>7056634</v>
+        <v>7056397</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2460,7 +2471,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2470,7 +2481,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2485,22 +2496,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121147410</v>
+        <v>121147479</v>
       </c>
       <c r="B18" t="n">
-        <v>98095</v>
+        <v>95392</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2509,42 +2520,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592612</v>
+        <v>592613</v>
       </c>
       <c r="R18" t="n">
-        <v>7056401</v>
+        <v>7056374</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2576,7 +2583,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2586,7 +2593,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2601,22 +2608,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121146590</v>
+        <v>121147489</v>
       </c>
       <c r="B19" t="n">
-        <v>90675</v>
+        <v>98098</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2625,38 +2632,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592518</v>
+        <v>592612</v>
       </c>
       <c r="R19" t="n">
-        <v>7056599</v>
+        <v>7056379</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2688,7 +2699,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2698,7 +2709,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2713,22 +2724,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121147630</v>
+        <v>121146569</v>
       </c>
       <c r="B20" t="n">
-        <v>79685</v>
+        <v>90999</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2741,21 +2752,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2765,10 +2776,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592484</v>
+        <v>592513</v>
       </c>
       <c r="R20" t="n">
-        <v>7056497</v>
+        <v>7056596</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2800,7 +2811,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2810,7 +2821,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2825,22 +2836,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121146575</v>
+        <v>121146485</v>
       </c>
       <c r="B21" t="n">
-        <v>79685</v>
+        <v>98098</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2849,38 +2860,42 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>592529</v>
+        <v>592495</v>
       </c>
       <c r="R21" t="n">
-        <v>7056593</v>
+        <v>7056643</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2912,7 +2927,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2922,7 +2937,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2949,10 +2964,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121146548</v>
+        <v>121146679</v>
       </c>
       <c r="B22" t="n">
-        <v>79685</v>
+        <v>90678</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2961,25 +2976,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2989,10 +3004,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>592514</v>
+        <v>592516</v>
       </c>
       <c r="R22" t="n">
-        <v>7056616</v>
+        <v>7056543</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3024,7 +3039,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3034,7 +3049,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3061,10 +3076,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121146272</v>
+        <v>121146641</v>
       </c>
       <c r="B23" t="n">
-        <v>79685</v>
+        <v>78607</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3077,21 +3092,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3101,10 +3116,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>592457</v>
+        <v>592519</v>
       </c>
       <c r="R23" t="n">
-        <v>7056760</v>
+        <v>7056540</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3136,7 +3151,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3146,7 +3161,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3161,22 +3176,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121146679</v>
+        <v>121146710</v>
       </c>
       <c r="B24" t="n">
-        <v>90675</v>
+        <v>78607</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3185,25 +3200,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3213,10 +3228,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592516</v>
+        <v>592531</v>
       </c>
       <c r="R24" t="n">
-        <v>7056543</v>
+        <v>7056489</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3248,7 +3263,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3258,7 +3273,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3273,22 +3288,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121147570</v>
+        <v>121146852</v>
       </c>
       <c r="B25" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3330,10 +3345,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>592521</v>
+        <v>592599</v>
       </c>
       <c r="R25" t="n">
-        <v>7056445</v>
+        <v>7056477</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3365,7 +3380,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3375,12 +3390,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3407,10 +3422,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121146852</v>
+        <v>121147583</v>
       </c>
       <c r="B26" t="n">
-        <v>57351</v>
+        <v>78607</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3423,39 +3438,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592599</v>
+        <v>592533</v>
       </c>
       <c r="R26" t="n">
-        <v>7056477</v>
+        <v>7056442</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3487,7 +3497,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3497,12 +3507,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3517,22 +3522,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121147437</v>
+        <v>121146592</v>
       </c>
       <c r="B27" t="n">
-        <v>57504</v>
+        <v>98098</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3541,35 +3546,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592631</v>
+        <v>592533</v>
       </c>
       <c r="R27" t="n">
-        <v>7056396</v>
+        <v>7056596</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3638,22 +3638,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121146430</v>
+        <v>121146572</v>
       </c>
       <c r="B28" t="n">
-        <v>98095</v>
+        <v>91153</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3666,38 +3666,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>592474</v>
+        <v>592530</v>
       </c>
       <c r="R28" t="n">
-        <v>7056672</v>
+        <v>7056612</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3729,7 +3725,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3739,7 +3735,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3754,22 +3750,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121146496</v>
+        <v>121146483</v>
       </c>
       <c r="B29" t="n">
-        <v>78604</v>
+        <v>57354</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3782,34 +3778,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>592472</v>
+        <v>592490</v>
       </c>
       <c r="R29" t="n">
-        <v>7056658</v>
+        <v>7056655</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3841,7 +3842,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3851,7 +3852,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3866,22 +3872,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121146507</v>
+        <v>121147410</v>
       </c>
       <c r="B30" t="n">
-        <v>57351</v>
+        <v>98098</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3890,31 +3896,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3923,10 +3928,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592490</v>
+        <v>592612</v>
       </c>
       <c r="R30" t="n">
-        <v>7056647</v>
+        <v>7056401</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3958,7 +3963,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3968,12 +3973,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 51337-2024 artfynd.xlsx
+++ b/artfynd/A 51337-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121147437</v>
+        <v>121146481</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>98098</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592631</v>
+        <v>592483</v>
       </c>
       <c r="R2" t="n">
-        <v>7056396</v>
+        <v>7056656</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,22 +779,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121146532</v>
+        <v>121147570</v>
       </c>
       <c r="B3" t="n">
-        <v>95392</v>
+        <v>57354</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,38 +803,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592507</v>
+        <v>592521</v>
       </c>
       <c r="R3" t="n">
-        <v>7056634</v>
+        <v>7056445</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121146272</v>
+        <v>121147479</v>
       </c>
       <c r="B4" t="n">
-        <v>79688</v>
+        <v>95392</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,25 +925,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592457</v>
+        <v>592613</v>
       </c>
       <c r="R4" t="n">
-        <v>7056760</v>
+        <v>7056374</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,19 +1013,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121146430</v>
+        <v>121146485</v>
       </c>
       <c r="B5" t="n">
         <v>98098</v>
@@ -1055,7 +1060,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1064,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592474</v>
+        <v>592495</v>
       </c>
       <c r="R5" t="n">
-        <v>7056672</v>
+        <v>7056643</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121147630</v>
+        <v>121147489</v>
       </c>
       <c r="B6" t="n">
-        <v>79688</v>
+        <v>98098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,38 +1153,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592484</v>
+        <v>592612</v>
       </c>
       <c r="R6" t="n">
-        <v>7056497</v>
+        <v>7056379</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,7 +1220,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1230,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1257,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121146507</v>
+        <v>121147431</v>
       </c>
       <c r="B7" t="n">
-        <v>57354</v>
+        <v>98098</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,31 +1269,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1293,10 +1301,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592490</v>
+        <v>592617</v>
       </c>
       <c r="R7" t="n">
-        <v>7056647</v>
+        <v>7056397</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,7 +1336,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,12 +1346,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,10 +1373,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121146481</v>
+        <v>121146679</v>
       </c>
       <c r="B8" t="n">
-        <v>98098</v>
+        <v>90678</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,42 +1385,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592483</v>
+        <v>592516</v>
       </c>
       <c r="R8" t="n">
-        <v>7056656</v>
+        <v>7056543</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1449,7 +1448,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1459,7 +1458,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,22 +1473,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121146339</v>
+        <v>121146496</v>
       </c>
       <c r="B9" t="n">
-        <v>91989</v>
+        <v>78607</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,25 +1497,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1526,10 +1525,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592379</v>
+        <v>592472</v>
       </c>
       <c r="R9" t="n">
-        <v>7056750</v>
+        <v>7056658</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1561,7 +1560,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,7 +1570,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,7 +1597,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121147570</v>
+        <v>121146507</v>
       </c>
       <c r="B10" t="n">
         <v>57354</v>
@@ -1643,10 +1642,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592521</v>
+        <v>592490</v>
       </c>
       <c r="R10" t="n">
-        <v>7056445</v>
+        <v>7056647</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,7 +1677,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1688,12 +1687,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,22 +1707,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121146683</v>
+        <v>121146548</v>
       </c>
       <c r="B11" t="n">
-        <v>90731</v>
+        <v>79688</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,21 +1735,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1760,10 +1759,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592517</v>
+        <v>592514</v>
       </c>
       <c r="R11" t="n">
-        <v>7056543</v>
+        <v>7056616</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,7 +1794,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1805,7 +1804,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1832,7 +1831,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121146575</v>
+        <v>121146704</v>
       </c>
       <c r="B12" t="n">
         <v>79688</v>
@@ -1872,10 +1871,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592529</v>
+        <v>592539</v>
       </c>
       <c r="R12" t="n">
-        <v>7056593</v>
+        <v>7056491</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1906,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1917,7 +1916,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,22 +1931,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121146704</v>
+        <v>121146483</v>
       </c>
       <c r="B13" t="n">
-        <v>79688</v>
+        <v>57354</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1960,34 +1959,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592539</v>
+        <v>592490</v>
       </c>
       <c r="R13" t="n">
-        <v>7056491</v>
+        <v>7056655</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,7 +2023,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2029,7 +2033,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,22 +2053,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121146496</v>
+        <v>121146852</v>
       </c>
       <c r="B14" t="n">
-        <v>78607</v>
+        <v>57354</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2072,34 +2081,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592472</v>
+        <v>592599</v>
       </c>
       <c r="R14" t="n">
-        <v>7056658</v>
+        <v>7056477</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2131,7 +2145,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2141,7 +2155,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,10 +2187,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121146590</v>
+        <v>121146683</v>
       </c>
       <c r="B15" t="n">
-        <v>90678</v>
+        <v>90731</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2180,25 +2199,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2208,10 +2227,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592518</v>
+        <v>592517</v>
       </c>
       <c r="R15" t="n">
-        <v>7056599</v>
+        <v>7056543</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2243,7 +2262,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2253,7 +2272,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,10 +2299,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121146548</v>
+        <v>121146339</v>
       </c>
       <c r="B16" t="n">
-        <v>79688</v>
+        <v>91989</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2292,25 +2311,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2320,10 +2339,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>592514</v>
+        <v>592379</v>
       </c>
       <c r="R16" t="n">
-        <v>7056616</v>
+        <v>7056750</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2355,7 +2374,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2365,7 +2384,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2392,10 +2411,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121147431</v>
+        <v>121146575</v>
       </c>
       <c r="B17" t="n">
-        <v>98098</v>
+        <v>79688</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2404,42 +2423,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>592617</v>
+        <v>592529</v>
       </c>
       <c r="R17" t="n">
-        <v>7056397</v>
+        <v>7056593</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2471,7 +2486,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2481,7 +2496,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2508,10 +2523,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121147479</v>
+        <v>121146572</v>
       </c>
       <c r="B18" t="n">
-        <v>95392</v>
+        <v>91153</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2520,25 +2535,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2869</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2548,10 +2563,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592613</v>
+        <v>592530</v>
       </c>
       <c r="R18" t="n">
-        <v>7056374</v>
+        <v>7056612</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2583,7 +2598,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2593,7 +2608,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2620,10 +2635,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121147489</v>
+        <v>121146532</v>
       </c>
       <c r="B19" t="n">
-        <v>98098</v>
+        <v>95392</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2632,42 +2647,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592612</v>
+        <v>592507</v>
       </c>
       <c r="R19" t="n">
-        <v>7056379</v>
+        <v>7056634</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2699,7 +2710,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2709,7 +2720,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2724,22 +2735,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121146569</v>
+        <v>121146710</v>
       </c>
       <c r="B20" t="n">
-        <v>90999</v>
+        <v>78607</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2752,21 +2763,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2776,10 +2787,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592513</v>
+        <v>592531</v>
       </c>
       <c r="R20" t="n">
-        <v>7056596</v>
+        <v>7056489</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2811,7 +2822,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2821,7 +2832,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2836,19 +2847,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121146485</v>
+        <v>121146430</v>
       </c>
       <c r="B21" t="n">
         <v>98098</v>
@@ -2883,7 +2894,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2892,10 +2903,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>592495</v>
+        <v>592474</v>
       </c>
       <c r="R21" t="n">
-        <v>7056643</v>
+        <v>7056672</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2927,7 +2938,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2937,7 +2948,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2964,10 +2975,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121146679</v>
+        <v>121146569</v>
       </c>
       <c r="B22" t="n">
-        <v>90678</v>
+        <v>90999</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2976,25 +2987,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3004,10 +3015,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>592516</v>
+        <v>592513</v>
       </c>
       <c r="R22" t="n">
-        <v>7056543</v>
+        <v>7056596</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3039,7 +3050,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3049,7 +3060,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3076,10 +3087,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121146641</v>
+        <v>121147410</v>
       </c>
       <c r="B23" t="n">
-        <v>78607</v>
+        <v>98098</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3088,38 +3099,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>592519</v>
+        <v>592612</v>
       </c>
       <c r="R23" t="n">
-        <v>7056540</v>
+        <v>7056401</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3151,7 +3166,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3161,7 +3176,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3176,22 +3191,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121146710</v>
+        <v>121147437</v>
       </c>
       <c r="B24" t="n">
-        <v>78607</v>
+        <v>57507</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3204,37 +3219,46 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592531</v>
+        <v>592631</v>
       </c>
       <c r="R24" t="n">
-        <v>7056489</v>
+        <v>7056396</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3263,7 +3287,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3273,7 +3297,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3288,22 +3312,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121146852</v>
+        <v>121146641</v>
       </c>
       <c r="B25" t="n">
-        <v>57354</v>
+        <v>78607</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3316,39 +3340,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>592599</v>
+        <v>592519</v>
       </c>
       <c r="R25" t="n">
-        <v>7056477</v>
+        <v>7056540</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3380,7 +3399,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3390,12 +3409,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3422,10 +3436,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121147583</v>
+        <v>121146592</v>
       </c>
       <c r="B26" t="n">
-        <v>78607</v>
+        <v>98098</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3434,28 +3448,32 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
@@ -3465,7 +3483,7 @@
         <v>592533</v>
       </c>
       <c r="R26" t="n">
-        <v>7056442</v>
+        <v>7056596</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3497,7 +3515,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3507,7 +3525,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3534,10 +3552,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121146592</v>
+        <v>121147583</v>
       </c>
       <c r="B27" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3546,32 +3564,28 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
@@ -3581,7 +3595,7 @@
         <v>592533</v>
       </c>
       <c r="R27" t="n">
-        <v>7056596</v>
+        <v>7056442</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3613,7 +3627,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3623,7 +3637,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3650,10 +3664,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121146572</v>
+        <v>121146590</v>
       </c>
       <c r="B28" t="n">
-        <v>91153</v>
+        <v>90678</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3662,25 +3676,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3690,10 +3704,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>592530</v>
+        <v>592518</v>
       </c>
       <c r="R28" t="n">
-        <v>7056612</v>
+        <v>7056599</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3725,7 +3739,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3735,7 +3749,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3762,10 +3776,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121146483</v>
+        <v>121146272</v>
       </c>
       <c r="B29" t="n">
-        <v>57354</v>
+        <v>79688</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3778,39 +3792,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>592490</v>
+        <v>592457</v>
       </c>
       <c r="R29" t="n">
-        <v>7056655</v>
+        <v>7056760</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3842,7 +3851,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3852,12 +3861,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:41</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3884,10 +3888,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121147410</v>
+        <v>121147630</v>
       </c>
       <c r="B30" t="n">
-        <v>98098</v>
+        <v>79688</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3896,42 +3900,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592612</v>
+        <v>592484</v>
       </c>
       <c r="R30" t="n">
-        <v>7056401</v>
+        <v>7056497</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3963,7 +3963,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 51337-2024 artfynd.xlsx
+++ b/artfynd/A 51337-2024 artfynd.xlsx
@@ -3552,10 +3552,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121147583</v>
+        <v>121146590</v>
       </c>
       <c r="B27" t="n">
-        <v>78607</v>
+        <v>90678</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3564,25 +3564,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592533</v>
+        <v>592518</v>
       </c>
       <c r="R27" t="n">
-        <v>7056442</v>
+        <v>7056599</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3627,7 +3627,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3652,22 +3652,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121146590</v>
+        <v>121146272</v>
       </c>
       <c r="B28" t="n">
-        <v>90678</v>
+        <v>79688</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3676,25 +3676,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>592518</v>
+        <v>592457</v>
       </c>
       <c r="R28" t="n">
-        <v>7056599</v>
+        <v>7056760</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3764,19 +3764,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121146272</v>
+        <v>121147630</v>
       </c>
       <c r="B29" t="n">
         <v>79688</v>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>592457</v>
+        <v>592484</v>
       </c>
       <c r="R29" t="n">
-        <v>7056760</v>
+        <v>7056497</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3888,10 +3888,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121147630</v>
+        <v>121147583</v>
       </c>
       <c r="B30" t="n">
-        <v>79688</v>
+        <v>78607</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3904,21 +3904,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592484</v>
+        <v>592533</v>
       </c>
       <c r="R30" t="n">
-        <v>7056497</v>
+        <v>7056442</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3963,7 +3963,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 51337-2024 artfynd.xlsx
+++ b/artfynd/A 51337-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121146481</v>
+        <v>121147570</v>
       </c>
       <c r="B2" t="n">
-        <v>98098</v>
+        <v>57354</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592483</v>
+        <v>592521</v>
       </c>
       <c r="R2" t="n">
-        <v>7056656</v>
+        <v>7056445</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,22 +785,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121147570</v>
+        <v>121146481</v>
       </c>
       <c r="B3" t="n">
-        <v>57354</v>
+        <v>98098</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,31 +809,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -836,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592521</v>
+        <v>592483</v>
       </c>
       <c r="R3" t="n">
-        <v>7056445</v>
+        <v>7056656</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,12 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,12 +901,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -3552,10 +3552,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121146590</v>
+        <v>121147583</v>
       </c>
       <c r="B27" t="n">
-        <v>90678</v>
+        <v>78607</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3564,25 +3564,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592518</v>
+        <v>592533</v>
       </c>
       <c r="R27" t="n">
-        <v>7056599</v>
+        <v>7056442</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3627,7 +3627,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3652,22 +3652,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121146272</v>
+        <v>121146590</v>
       </c>
       <c r="B28" t="n">
-        <v>79688</v>
+        <v>90678</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3676,25 +3676,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>592457</v>
+        <v>592518</v>
       </c>
       <c r="R28" t="n">
-        <v>7056760</v>
+        <v>7056599</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3764,19 +3764,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121147630</v>
+        <v>121146272</v>
       </c>
       <c r="B29" t="n">
         <v>79688</v>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>592484</v>
+        <v>592457</v>
       </c>
       <c r="R29" t="n">
-        <v>7056497</v>
+        <v>7056760</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3888,10 +3888,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121147583</v>
+        <v>121147630</v>
       </c>
       <c r="B30" t="n">
-        <v>78607</v>
+        <v>79688</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3904,21 +3904,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592533</v>
+        <v>592484</v>
       </c>
       <c r="R30" t="n">
-        <v>7056442</v>
+        <v>7056497</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3963,7 +3963,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD30" t="b">
